--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2430-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2430-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96F76FDC-EA38-4EDE-82A4-61DC2547278B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2214AB9B-DE46-404D-BC60-1B050295AA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{1F0309A0-68F5-4119-86AD-C702F974869B}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{FDE5D662-7EC0-432F-9ED0-7C207F72E9C4}"/>
   </bookViews>
   <sheets>
     <sheet name="2430-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1583,29 +1583,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AB19471-084C-4429-A755-C2BD91DB9F33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69722863-9697-4B49-86EA-9B6D894AC424}">
   <dimension ref="A1:X43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1638,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1675,7 +1674,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1727,7 +1726,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1795,7 +1794,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2024</v>
       </c>
@@ -1867,7 +1866,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>2023</v>
       </c>
@@ -1939,7 +1938,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2022</v>
       </c>
@@ -2011,7 +2010,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2021</v>
       </c>
@@ -2083,7 +2082,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2020</v>
       </c>
@@ -2155,7 +2154,7 @@
         <v>8.0500000000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2019</v>
       </c>
@@ -2227,7 +2226,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>2018</v>
       </c>
@@ -2299,7 +2298,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="41">
         <v>2017</v>
       </c>
@@ -2371,7 +2370,7 @@
         <v>7.16</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2016</v>
       </c>
@@ -2443,7 +2442,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="41">
         <v>2015</v>
       </c>
@@ -2515,7 +2514,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2014</v>
       </c>
@@ -2587,7 +2586,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2013</v>
       </c>
@@ -2659,7 +2658,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2012</v>
       </c>
@@ -2731,7 +2730,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="41">
         <v>2011</v>
       </c>
@@ -2803,7 +2802,7 @@
         <v>8.11</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2010</v>
       </c>
@@ -2875,7 +2874,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="43">
         <v>2009</v>
       </c>
@@ -2947,7 +2946,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="45"/>
       <c r="B21" s="46"/>
       <c r="C21" s="20" t="s">
@@ -2975,7 +2974,7 @@
       <c r="W21" s="52"/>
       <c r="X21" s="48"/>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2008</v>
       </c>
@@ -3047,7 +3046,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="43">
         <v>2007</v>
       </c>
@@ -3119,7 +3118,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="45"/>
       <c r="B24" s="46"/>
       <c r="C24" s="20" t="s">
@@ -3147,7 +3146,7 @@
       <c r="W24" s="52"/>
       <c r="X24" s="48"/>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2006</v>
       </c>
@@ -3219,7 +3218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="43">
         <v>2005</v>
       </c>
@@ -3291,7 +3290,7 @@
         <v>9.89</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="45"/>
       <c r="B27" s="46"/>
       <c r="C27" s="20" t="s">
@@ -3319,7 +3318,7 @@
       <c r="W27" s="52"/>
       <c r="X27" s="48"/>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="53">
         <v>2004</v>
       </c>
@@ -3391,7 +3390,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="55"/>
       <c r="B29" s="56"/>
       <c r="C29" s="22" t="s">
@@ -3419,7 +3418,7 @@
       <c r="W29" s="62"/>
       <c r="X29" s="58"/>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="43">
         <v>2003</v>
       </c>
@@ -3491,7 +3490,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="45"/>
       <c r="B31" s="46"/>
       <c r="C31" s="20" t="s">
@@ -3519,7 +3518,7 @@
       <c r="W31" s="52"/>
       <c r="X31" s="48"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2002</v>
       </c>
@@ -3591,7 +3590,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="41">
         <v>2001</v>
       </c>
@@ -3663,7 +3662,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2000</v>
       </c>
@@ -3735,7 +3734,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>1999</v>
       </c>
@@ -3807,7 +3806,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1998</v>
       </c>
@@ -3879,7 +3878,7 @@
         <v>8.42</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="41">
         <v>1997</v>
       </c>
@@ -3951,7 +3950,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>1996</v>
       </c>
@@ -4023,7 +4022,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="41">
         <v>1995</v>
       </c>
@@ -4095,7 +4094,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>1994</v>
       </c>
@@ -4167,7 +4166,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="41">
         <v>1993</v>
       </c>
@@ -4239,7 +4238,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>1992</v>
       </c>
@@ -4311,7 +4310,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="41" t="s">
         <v>61</v>
       </c>
